--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484117_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484117_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6324</v>
+        <v>5.4143</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3233</v>
+        <v>3.0596</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3091</v>
+        <v>2.3548</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2334</v>
+        <v>2.207</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5582</v>
+        <v>1.4867</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6752</v>
+        <v>0.7204</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8762</v>
+        <v>1.7794</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1533</v>
+        <v>1.7392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7229</v>
+        <v>0.0402</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3572</v>
+        <v>0.4277</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5951</v>
+        <v>-0.2525</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9523</v>
+        <v>0.6802</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5298</v>
+        <v>0.6121</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0973</v>
+        <v>0.0737</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4324</v>
+        <v>0.5384</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9405</v>
+        <v>1.2065</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6797</v>
+        <v>4.232</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5494</v>
+        <v>1.8948</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1303</v>
+        <v>2.3372</v>
       </c>
       <c r="G3" t="n">
-        <v>2.207</v>
+        <v>5.2334</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4867</v>
+        <v>3.5582</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7204</v>
+        <v>1.6752</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7794</v>
+        <v>4.8762</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7392</v>
+        <v>4.1533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0402</v>
+        <v>0.7229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4277</v>
+        <v>0.3572</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2525</v>
+        <v>-0.5951</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6802</v>
+        <v>0.9523</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1224</v>
+        <v>1.1294</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4364</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.314</v>
+        <v>0.4605</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>-0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>-0.6745</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2895</v>
+        <v>4.0157</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2002</v>
+        <v>3.7753</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0893</v>
+        <v>0.2404</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8991</v>
+        <v>1.4442</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1768</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0759</v>
+        <v>1.4342</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0107</v>
+        <v>2.359</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.249</v>
+        <v>1.0739</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2597</v>
+        <v>1.2852</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1116</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9278</v>
+        <v>-1.0639</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8162</v>
+        <v>0.149</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2596</v>
+        <v>0.2423</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1814</v>
+        <v>0.2098</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.266</v>
+        <v>0.9405</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
         <v>-0.266</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1346</v>
+        <v>3.3558</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2028</v>
+        <v>2.0982</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0682</v>
+        <v>1.2576</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4442</v>
+        <v>2.8991</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>-2.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4342</v>
+        <v>5.0759</v>
       </c>
       <c r="J5" t="n">
-        <v>2.359</v>
+        <v>3.0107</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0739</v>
+        <v>-1.249</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2852</v>
+        <v>4.2597</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.1116</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0639</v>
+        <v>-0.9278</v>
       </c>
       <c r="O5" t="n">
-        <v>0.149</v>
+        <v>0.8162</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
         <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6388</v>
+        <v>0.3259</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3627</v>
+        <v>0.0794</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2761</v>
+        <v>0.2465</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9405</v>
+        <v>-0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1054</v>
+        <v>3.2047</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1446</v>
+        <v>3.0855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9608</v>
+        <v>0.1192</v>
       </c>
       <c r="G6" t="n">
         <v>-2.3212</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2752</v>
+        <v>1.3745</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3514</v>
+        <v>0.5896</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6266</v>
+        <v>0.7849</v>
       </c>
       <c r="V6" t="n">
         <v>4.1513</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4514</v>
+        <v>3.158</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0759</v>
+        <v>0.586</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3756</v>
+        <v>2.572</v>
       </c>
       <c r="G7" t="n">
         <v>1.0679</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4019</v>
+        <v>0.3047</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4988</v>
+        <v>0.0114</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0969</v>
+        <v>0.2933</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0043</v>
+        <v>2.236</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1087</v>
+        <v>0.7302</v>
       </c>
       <c r="F8" t="n">
-        <v>1.113</v>
+        <v>1.5058</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4082</v>
@@ -1074,13 +1074,13 @@
         <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9681</v>
+        <v>0.2636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6121</v>
+        <v>0.2268</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.356</v>
+        <v>0.0368</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1107,13 +1107,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0043</v>
+        <v>2.236</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1087</v>
+        <v>0.7302</v>
       </c>
       <c r="F9" t="n">
-        <v>1.113</v>
+        <v>1.5058</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4082</v>
@@ -1152,13 +1152,13 @@
         <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9681</v>
+        <v>0.2636</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6121</v>
+        <v>0.2268</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.356</v>
+        <v>0.0368</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,73 +1185,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6318</v>
+        <v>0.8051</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6561</v>
+        <v>1.0278</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0243</v>
+        <v>-0.2226</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3253</v>
+        <v>-0.3965</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7228</v>
+        <v>0.2772</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6024</v>
+        <v>-0.6737</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3253</v>
+        <v>0.6706</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7228</v>
+        <v>1.3508</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6024</v>
+        <v>-0.6802</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.0672</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.0737</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9758</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6952</v>
+        <v>0.4081</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0406</v>
+        <v>0.3571</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6546</v>
+        <v>0.051</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,73 +1263,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2224</v>
+        <v>0.3687</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5573</v>
+        <v>-1.2782</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3348</v>
+        <v>1.6469</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3965</v>
+        <v>0.416</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2772</v>
+        <v>1.6429</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6737</v>
+        <v>-1.2269</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6706</v>
+        <v>1.049</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3508</v>
+        <v>2.9691</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6802</v>
+        <v>-1.9201</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0672</v>
+        <v>-0.633</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0737</v>
+        <v>-1.3262</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0065</v>
+        <v>0.6932</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7935</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1746</v>
+        <v>0.6589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1133</v>
+        <v>0.0454</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0612</v>
+        <v>0.6135</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2777</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,67 +1341,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.157</v>
+        <v>-0.8731</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6863</v>
+        <v>1.4317</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8433</v>
+        <v>-2.3048</v>
       </c>
       <c r="G12" t="n">
-        <v>0.416</v>
+        <v>3.3253</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6429</v>
+        <v>2.7228</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2269</v>
+        <v>0.6024</v>
       </c>
       <c r="J12" t="n">
-        <v>1.049</v>
+        <v>3.3253</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9691</v>
+        <v>2.7228</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9201</v>
+        <v>0.6024</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.633</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3262</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6932</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4471</v>
+        <v>1.1903</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3627</v>
+        <v>0.8162</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8099</v>
+        <v>0.3741</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2777</v>
+        <v>-2.4129</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6745</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="13">
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1974</v>
+        <v>-1.0649</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2259</v>
+        <v>0.3303</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4233</v>
+        <v>-1.3953</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0388</v>
@@ -1464,13 +1464,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6512</v>
+        <v>0.7836</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0009</v>
+        <v>1.1053</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3498</v>
+        <v>-0.3217</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.3407</v>
+        <v>-3.012</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5863</v>
+        <v>-1.2575</v>
       </c>
       <c r="F14" t="n">
         <v>-1.7545</v>
@@ -1542,10 +1542,10 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6461</v>
+        <v>0.9749</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3288</v>
+        <v>0.6576</v>
       </c>
       <c r="U14" t="n">
         <v>0.3173</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>21.7747</v>
+        <v>24.0763</v>
       </c>
       <c r="E15" t="n">
-        <v>14.4455</v>
+        <v>16.2139</v>
       </c>
       <c r="F15" t="n">
-        <v>7.3293</v>
+        <v>7.862500000000001</v>
       </c>
       <c r="G15" t="n">
         <v>11.017</v>
@@ -1620,13 +1620,13 @@
         <v>19.2433</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2303</v>
+        <v>8.5319</v>
       </c>
       <c r="T15" t="n">
-        <v>3.299500000000001</v>
+        <v>5.068</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9308</v>
+        <v>3.463900000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.1469</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.9016</v>
       </c>
       <c r="E16" t="n">
         <v>2.2375</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4719</v>
+        <v>-1.3359</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5333</v>
@@ -1698,13 +1698,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7708</v>
+        <v>-0.6348</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3683</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4025</v>
+        <v>-0.2665</v>
       </c>
       <c r="V16" t="n">
         <v>0.4826</v>
@@ -1719,7 +1719,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,73 +1731,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3405</v>
+        <v>0.7962</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3784</v>
+        <v>-0.3185</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0379</v>
+        <v>1.1147</v>
       </c>
       <c r="G17" t="n">
-        <v>4.588</v>
+        <v>-0.9775</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0453</v>
+        <v>0.3829</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4573</v>
+        <v>-1.3604</v>
       </c>
       <c r="J17" t="n">
-        <v>7.7125</v>
+        <v>-0.9922</v>
       </c>
       <c r="K17" t="n">
-        <v>7.1075</v>
+        <v>1.0484</v>
       </c>
       <c r="L17" t="n">
-        <v>0.605</v>
+        <v>-2.0406</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1245</v>
+        <v>0.0147</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0622</v>
+        <v>-0.6655</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0623</v>
+        <v>0.6802</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1741</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.3564</v>
+        <v>-0.1984</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2186</v>
+        <v>-0.3571</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2436</v>
+        <v>-0.3344</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.975</v>
+        <v>-0.0227</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1453</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1206</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,67 +1809,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3099</v>
+        <v>0.7571</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4205</v>
+        <v>2.3784</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7304</v>
+        <v>-1.6213</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9775</v>
+        <v>4.588</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3829</v>
+        <v>5.0453</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3604</v>
+        <v>-0.4573</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9922</v>
+        <v>7.7125</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0484</v>
+        <v>7.1075</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0406</v>
+        <v>0.605</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0147</v>
+        <v>-3.1245</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6655</v>
+        <v>-2.0622</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6802</v>
+        <v>-1.0623</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-5.3564</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8434</v>
+        <v>-0.802</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4364</v>
+        <v>-0.2436</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.407</v>
+        <v>-0.5584</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9405</v>
+        <v>0.1453</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="19">
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0956</v>
+        <v>-0.2444</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8511</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.6067</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1416</v>
@@ -1932,13 +1932,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5243</v>
+        <v>-0.6731</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5667</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0424</v>
+        <v>-0.1064</v>
       </c>
       <c r="V19" t="n">
         <v>0.38</v>
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6</v>
+        <v>-0.9282</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5693</v>
+        <v>0.1612</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1693</v>
+        <v>-1.0894</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7383</v>
@@ -2010,13 +2010,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2585</v>
+        <v>-0.5867</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2551</v>
+        <v>-0.153</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.4337</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2938</v>
+        <v>-1.9741</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4907</v>
+        <v>-2.0825</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1969</v>
+        <v>0.1085</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4833</v>
@@ -2088,13 +2088,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7675</v>
+        <v>-0.4478</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8728</v>
+        <v>-0.4647</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1054</v>
+        <v>0.017</v>
       </c>
       <c r="V21" t="n">
         <v>0.1634</v>
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3925</v>
+        <v>-2.6807</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4919</v>
+        <v>-0.696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9005</v>
+        <v>-1.9847</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4266</v>
@@ -2166,13 +2166,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3407</v>
+        <v>0.0524</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1814</v>
+        <v>-0.0226</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1592</v>
+        <v>0.0751</v>
       </c>
       <c r="V22" t="n">
         <v>0.6773</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2967</v>
+        <v>-3.1683</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3608</v>
+        <v>-2.5648</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9359</v>
+        <v>-0.6035</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0927</v>
@@ -2244,13 +2244,13 @@
         <v>1.9838</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8156</v>
+        <v>-0.6872</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1926</v>
+        <v>-0.3967</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.623</v>
+        <v>-0.2905</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3803</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. NINOT PEDROSA</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,73 +2277,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5388</v>
+        <v>-3.4066</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4451</v>
+        <v>-2.3956</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.9838</v>
+        <v>-1.011</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.161</v>
+        <v>-3.3117</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2218</v>
+        <v>-1.2349</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0608</v>
+        <v>-2.0768</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4454</v>
+        <v>-1.5167</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3158</v>
+        <v>-0.2366</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1296</v>
+        <v>-1.2801</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6064</v>
+        <v>-1.795</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5376</v>
+        <v>-0.9983</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0688</v>
+        <v>-0.7967</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4313</v>
+        <v>-0.3854</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1304</v>
+        <v>-0.153</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5617</v>
+        <v>-0.2324</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.74</v>
+        <v>0.0921</v>
       </c>
       <c r="W24" t="n">
         <v>0.266</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.006</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>M. NINOT PEDROSA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,67 +2355,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8148</v>
+        <v>-3.5226</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8038</v>
+        <v>2.241</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.011</v>
+        <v>-5.7636</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3117</v>
+        <v>-0.161</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2349</v>
+        <v>-0.2218</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0768</v>
+        <v>0.0608</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.5167</v>
+        <v>2.4454</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2366</v>
+        <v>1.3158</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2801</v>
+        <v>1.1296</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.795</v>
+        <v>-2.6064</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9983</v>
+        <v>-1.5376</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7967</v>
+        <v>-1.0688</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="R25" t="n">
         <v>1.1903</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7935</v>
+        <v>-0.4152</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5611</v>
+        <v>-0.0736</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2324</v>
+        <v>-0.3415</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0921</v>
+        <v>-3.74</v>
       </c>
       <c r="W25" t="n">
         <v>0.266</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1738</v>
+        <v>-4.006</v>
       </c>
     </row>
     <row r="26">
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.1543</v>
+        <v>-5.94</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4278</v>
+        <v>-4.3258</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7265</v>
+        <v>-1.6142</v>
       </c>
       <c r="G26" t="n">
         <v>-3.1471</v>
@@ -2478,13 +2478,13 @@
         <v>0.1984</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1155</v>
+        <v>-0.9012</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6121</v>
+        <v>-0.5101</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5034</v>
+        <v>-0.3912</v>
       </c>
       <c r="V26" t="n">
         <v>0.0921</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.7705</v>
+        <v>-19.41</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.216299999999999</v>
+        <v>-6.216200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.554</v>
+        <v>-13.1937</v>
       </c>
       <c r="G27" t="n">
         <v>-11.4251</v>
@@ -2526,7 +2526,7 @@
         <v>-4.688000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.7369</v>
+        <v>-6.736899999999999</v>
       </c>
       <c r="J27" t="n">
         <v>8.452</v>
@@ -2547,7 +2547,7 @@
         <v>-1.878</v>
       </c>
       <c r="P27" t="n">
-        <v>9.999999999932285e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.8627</v>
@@ -2556,13 +2556,13 @@
         <v>16.8626</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.198300000000001</v>
+        <v>-5.8381</v>
       </c>
       <c r="T27" t="n">
         <v>-3.2867</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.9116</v>
+        <v>-2.5512</v>
       </c>
       <c r="V27" t="n">
         <v>-2.147000000000001</v>
